--- a/public/downloads/SarkerPrediction2023.xlsx
+++ b/public/downloads/SarkerPrediction2023.xlsx
@@ -8,29 +8,31 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="3" r:id="rId3"/>
-    <sheet name="CHGNetv0.3.0" sheetId="4" r:id="rId4"/>
-    <sheet name="DPA-3.1-3M-FT" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="GRACE-2L-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="MACE-MPA-0" sheetId="9" r:id="rId9"/>
-    <sheet name="MATLANTISv8" sheetId="10" r:id="rId10"/>
-    <sheet name="MatterSim_v1_5M" sheetId="11" r:id="rId11"/>
-    <sheet name="ORB-v3" sheetId="12" r:id="rId12"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="13" r:id="rId13"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="14" r:id="rId14"/>
-    <sheet name="UMA-m-1p1_omat" sheetId="15" r:id="rId15"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="16" r:id="rId16"/>
-    <sheet name="UMA-s-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="5" r:id="rId5"/>
+    <sheet name="CHGNetv0.3.0" sheetId="6" r:id="rId6"/>
+    <sheet name="DPA-3.1-3M-FT" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="GRACE-2L-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="MACE-MPA-0" sheetId="11" r:id="rId11"/>
+    <sheet name="MATLANTISv8" sheetId="12" r:id="rId12"/>
+    <sheet name="MatterSim_v1_5M" sheetId="13" r:id="rId13"/>
+    <sheet name="ORB-v3" sheetId="14" r:id="rId14"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="15" r:id="rId15"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="16" r:id="rId16"/>
+    <sheet name="UMA-m-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="18" r:id="rId18"/>
+    <sheet name="UMA-s-1p1_omat" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="55">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -62,10 +64,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -165,6 +167,27 @@
   </si>
   <si>
     <t>Adsorbate_name</t>
+  </si>
+  <si>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
   </si>
   <si>
     <t>O</t>
@@ -659,10 +682,10 @@
         <v>34</v>
       </c>
       <c r="N3" s="5">
-        <v>228.7915854454041</v>
+        <v>228791.5854454041</v>
       </c>
       <c r="O3" s="4">
-        <v>0.03774193095437216</v>
+        <v>37.74193095437217</v>
       </c>
       <c r="P3" s="5">
         <v>6062</v>
@@ -709,10 +732,10 @@
         <v>34</v>
       </c>
       <c r="N4" s="5">
-        <v>626.9190261363983</v>
+        <v>626919.0261363983</v>
       </c>
       <c r="O4" s="4">
-        <v>0.1098508894579286</v>
+        <v>109.8508894579286</v>
       </c>
       <c r="P4" s="5">
         <v>5707</v>
@@ -759,10 +782,10 @@
         <v>34</v>
       </c>
       <c r="N5" s="5">
-        <v>685.4857110977173</v>
+        <v>685485.7110977173</v>
       </c>
       <c r="O5" s="4">
-        <v>0.1600480296749281</v>
+        <v>160.0480296749282</v>
       </c>
       <c r="P5" s="5">
         <v>4283</v>
@@ -809,10 +832,10 @@
         <v>34</v>
       </c>
       <c r="N6" s="5">
-        <v>766.9275109767914</v>
+        <v>766927.5109767914</v>
       </c>
       <c r="O6" s="4">
-        <v>0.107262588947803</v>
+        <v>107.262588947803</v>
       </c>
       <c r="P6" s="5">
         <v>7150</v>
@@ -859,10 +882,10 @@
         <v>34</v>
       </c>
       <c r="N7" s="5">
-        <v>2260.681818246841</v>
+        <v>2260681.818246841</v>
       </c>
       <c r="O7" s="4">
-        <v>0.5252513518231509</v>
+        <v>525.2513518231509</v>
       </c>
       <c r="P7" s="5">
         <v>4304</v>
@@ -909,10 +932,10 @@
         <v>34</v>
       </c>
       <c r="N8" s="5">
-        <v>155.8559422492981</v>
+        <v>155855.9422492981</v>
       </c>
       <c r="O8" s="4">
-        <v>0.03189194643938983</v>
+        <v>31.89194643938983</v>
       </c>
       <c r="P8" s="5">
         <v>4887</v>
@@ -959,10 +982,10 @@
         <v>34</v>
       </c>
       <c r="N9" s="5">
-        <v>217.2792935371399</v>
+        <v>217279.2935371399</v>
       </c>
       <c r="O9" s="4">
-        <v>0.04103480520059299</v>
+        <v>41.03480520059299</v>
       </c>
       <c r="P9" s="5">
         <v>5295</v>
@@ -1009,10 +1032,10 @@
         <v>34</v>
       </c>
       <c r="N10" s="5">
-        <v>452.0728783607483</v>
+        <v>452072.8783607483</v>
       </c>
       <c r="O10" s="4">
-        <v>0.08284274846266232</v>
+        <v>82.84274846266231</v>
       </c>
       <c r="P10" s="5">
         <v>5457</v>
@@ -1059,10 +1082,10 @@
         <v>34</v>
       </c>
       <c r="N11" s="5">
-        <v>281.1073083877563</v>
+        <v>281107.3083877563</v>
       </c>
       <c r="O11" s="4">
-        <v>0.0516266865725907</v>
+        <v>51.62668657259069</v>
       </c>
       <c r="P11" s="5">
         <v>5445</v>
@@ -1109,10 +1132,10 @@
         <v>34</v>
       </c>
       <c r="N12" s="5">
-        <v>153.8095681667328</v>
+        <v>153809.5681667328</v>
       </c>
       <c r="O12" s="4">
-        <v>0.03096629115496936</v>
+        <v>30.96629115496936</v>
       </c>
       <c r="P12" s="5">
         <v>4967</v>
@@ -1159,10 +1182,10 @@
         <v>34</v>
       </c>
       <c r="N13" s="5">
-        <v>389.8551921844482</v>
+        <v>389855.1921844482</v>
       </c>
       <c r="O13" s="4">
-        <v>0.07654725941182962</v>
+        <v>76.54725941182961</v>
       </c>
       <c r="P13" s="5">
         <v>5093</v>
@@ -1209,10 +1232,10 @@
         <v>34</v>
       </c>
       <c r="N14" s="5">
-        <v>5502.86586022377</v>
+        <v>5502865.86022377</v>
       </c>
       <c r="O14" s="4">
-        <v>0.6875144752903261</v>
+        <v>687.514475290326</v>
       </c>
       <c r="P14" s="5">
         <v>8004</v>
@@ -1259,10 +1282,10 @@
         <v>34</v>
       </c>
       <c r="N15" s="5">
-        <v>3721.835453987122</v>
+        <v>3721835.453987122</v>
       </c>
       <c r="O15" s="4">
-        <v>0.7388992364477113</v>
+        <v>738.8992364477112</v>
       </c>
       <c r="P15" s="5">
         <v>5037</v>
@@ -1309,10 +1332,10 @@
         <v>34</v>
       </c>
       <c r="N16" s="5">
-        <v>1134.688172340393</v>
+        <v>1134688.172340393</v>
       </c>
       <c r="O16" s="4">
-        <v>0.1293239311990418</v>
+        <v>129.3239311990419</v>
       </c>
       <c r="P16" s="5">
         <v>8774</v>
@@ -1359,10 +1382,10 @@
         <v>34</v>
       </c>
       <c r="N17" s="5">
-        <v>639.0788025856018</v>
+        <v>639078.8025856018</v>
       </c>
       <c r="O17" s="4">
-        <v>0.1359742133160855</v>
+        <v>135.9742133160855</v>
       </c>
       <c r="P17" s="5">
         <v>4700</v>
@@ -1390,7 +1413,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1401,9 +1424,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1437,8 +1466,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1460,75 +1497,111 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.5736767769419325</v>
+        <v>0.9889725316759489</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4912602857510781</v>
+        <v>0.6077639389531091</v>
       </c>
       <c r="D3" s="4">
-        <v>0.6459236660598786</v>
+        <v>0.8355656296946063</v>
       </c>
       <c r="E3" s="4">
-        <v>89.72562358276643</v>
+        <v>89.23809523809523</v>
       </c>
       <c r="F3" s="4">
-        <v>80.75988068605604</v>
+        <v>82.24161073825488</v>
       </c>
       <c r="G3" s="5">
         <v>15</v>
       </c>
       <c r="H3" s="5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I3" s="5">
+        <v>1</v>
+      </c>
+      <c r="J3" s="5">
+        <v>4</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>1</v>
+      </c>
+      <c r="M3" s="5">
         <v>3</v>
       </c>
-      <c r="J3" s="5">
-        <v>1</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>1</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.5305578991571226</v>
+      </c>
+      <c r="O3" s="5">
+        <v>13</v>
+      </c>
+      <c r="P3" s="4">
+        <v>1.017571473039275</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>1.017008309910844</v>
+      </c>
+      <c r="R3" s="5">
+        <v>13</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4500394426294582</v>
+        <v>0.6878769108145679</v>
       </c>
       <c r="C4" s="4">
-        <v>0.4500394426294582</v>
+        <v>0.6710727535371608</v>
       </c>
       <c r="D4" s="4">
-        <v>0.4932994550387989</v>
+        <v>0.5899931000737741</v>
       </c>
       <c r="E4" s="4">
-        <v>89.78571428571429</v>
+        <v>88.62244897959184</v>
       </c>
       <c r="F4" s="4">
-        <v>85.0089485458613</v>
+        <v>79.19463087248322</v>
       </c>
       <c r="G4" s="5">
         <v>10</v>
       </c>
       <c r="H4" s="5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="5">
         <v>0</v>
@@ -1542,25 +1615,43 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.130914128998574</v>
+      </c>
+      <c r="O4" s="5">
+        <v>9</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.6616940850148531</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.6565267392039859</v>
+      </c>
+      <c r="R4" s="5">
+        <v>9</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.6429144995228651</v>
+        <v>0.5433500928570432</v>
       </c>
       <c r="C5" s="4">
-        <v>0.6429144995228651</v>
+        <v>0.5433500928570432</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2573758948499805</v>
+        <v>0.452993599078237</v>
       </c>
       <c r="E5" s="4">
-        <v>86.9047619047619</v>
+        <v>87.14285714285714</v>
       </c>
       <c r="F5" s="4">
-        <v>81.84563758389265</v>
+        <v>83.668903803132</v>
       </c>
       <c r="G5" s="5">
         <v>9</v>
@@ -1583,9 +1674,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.4622175358743278</v>
+      </c>
+      <c r="O5" s="5">
+        <v>9</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3526539650287899</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3526539650287899</v>
+      </c>
+      <c r="R5" s="5">
+        <v>9</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1596,6 +1705,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1603,7 +1713,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1614,9 +1724,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1650,8 +1766,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1673,75 +1797,111 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.717473649266384</v>
+        <v>1.021245510080191</v>
       </c>
       <c r="C3" s="4">
-        <v>0.6327272717123046</v>
+        <v>0.9344672499660689</v>
       </c>
       <c r="D3" s="4">
-        <v>0.7987990083994816</v>
+        <v>0.7421182182424388</v>
       </c>
       <c r="E3" s="4">
-        <v>90.31972789115648</v>
+        <v>87.36734693877551</v>
       </c>
       <c r="F3" s="4">
-        <v>83.54809843400439</v>
+        <v>82.86577181208038</v>
       </c>
       <c r="G3" s="5">
         <v>15</v>
       </c>
       <c r="H3" s="5">
+        <v>12</v>
+      </c>
+      <c r="I3" s="5">
+        <v>1</v>
+      </c>
+      <c r="J3" s="5">
+        <v>2</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>1</v>
+      </c>
+      <c r="M3" s="5">
+        <v>1</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.3496225510211253</v>
+      </c>
+      <c r="O3" s="5">
         <v>13</v>
       </c>
-      <c r="I3" s="5">
-        <v>1</v>
-      </c>
-      <c r="J3" s="5">
-        <v>1</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>1</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="P3" s="4">
+        <v>1.044553680148266</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>1.051402389077328</v>
+      </c>
+      <c r="R3" s="5">
+        <v>13</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4720091069726579</v>
+        <v>0.7168151479347017</v>
       </c>
       <c r="C4" s="4">
-        <v>0.5108903683099426</v>
+        <v>0.7168151479347017</v>
       </c>
       <c r="D4" s="4">
-        <v>0.5440246945054042</v>
+        <v>0.6354155164344576</v>
       </c>
       <c r="E4" s="4">
-        <v>89</v>
+        <v>87.68367346938776</v>
       </c>
       <c r="F4" s="4">
-        <v>79.32997762863542</v>
+        <v>87.11409395973155</v>
       </c>
       <c r="G4" s="5">
         <v>10</v>
       </c>
       <c r="H4" s="5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" s="5">
         <v>0</v>
@@ -1755,25 +1915,43 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.1939627669703924</v>
+      </c>
+      <c r="O4" s="5">
+        <v>10</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.6780225945406231</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.6780225945406231</v>
+      </c>
+      <c r="R4" s="5">
+        <v>10</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.776694773288543</v>
+        <v>0.6868712014722733</v>
       </c>
       <c r="C5" s="4">
-        <v>0.7509882748092119</v>
+        <v>0.8787955741052732</v>
       </c>
       <c r="D5" s="4">
-        <v>0.3937377261818382</v>
+        <v>0.7026666824915411</v>
       </c>
       <c r="E5" s="4">
-        <v>85.18518518518516</v>
+        <v>83.30309901738471</v>
       </c>
       <c r="F5" s="4">
-        <v>69.59358687546508</v>
+        <v>72.93686303753378</v>
       </c>
       <c r="G5" s="5">
         <v>9</v>
@@ -1782,13 +1960,13 @@
         <v>6</v>
       </c>
       <c r="I5" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" s="5">
         <v>0</v>
@@ -1796,9 +1974,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.8585792498948498</v>
+      </c>
+      <c r="O5" s="5">
+        <v>6</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.457374077277231</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3833820402778024</v>
+      </c>
+      <c r="R5" s="5">
+        <v>6</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1809,6 +2005,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1816,7 +2013,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1827,9 +2024,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1863,8 +2066,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1886,34 +2097,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.6954385844553315</v>
+        <v>0.5736767769419325</v>
       </c>
       <c r="C3" s="4">
-        <v>0.5733904500777892</v>
+        <v>0.4912602857510781</v>
       </c>
       <c r="D3" s="4">
-        <v>0.721273548675028</v>
+        <v>0.6459236660598786</v>
       </c>
       <c r="E3" s="4">
-        <v>90.59183673469387</v>
+        <v>89.72562358276643</v>
       </c>
       <c r="F3" s="4">
-        <v>82.90454884414596</v>
+        <v>80.75988068605604</v>
       </c>
       <c r="G3" s="5">
         <v>15</v>
       </c>
       <c r="H3" s="5">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J3" s="5">
         <v>1</v>
@@ -1927,25 +2156,43 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.01756953263081843</v>
+      </c>
+      <c r="O3" s="5">
+        <v>11</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.5701628704157689</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.4896630555119127</v>
+      </c>
+      <c r="R3" s="5">
+        <v>11</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4625028813867204</v>
+        <v>0.4500394426294582</v>
       </c>
       <c r="C4" s="4">
-        <v>0.4625028813867204</v>
+        <v>0.4500394426294582</v>
       </c>
       <c r="D4" s="4">
-        <v>0.5796379452378261</v>
+        <v>0.4932994550387989</v>
       </c>
       <c r="E4" s="4">
-        <v>90.87414965986395</v>
+        <v>89.78571428571429</v>
       </c>
       <c r="F4" s="4">
-        <v>84.079418344519</v>
+        <v>85.0089485458613</v>
       </c>
       <c r="G4" s="5">
         <v>10</v>
@@ -1968,34 +2215,52 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.2465610009057906</v>
+      </c>
+      <c r="O4" s="5">
+        <v>10</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.415590272258642</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.415590272258642</v>
+      </c>
+      <c r="R4" s="5">
+        <v>10</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.4717097158533584</v>
+        <v>0.6429144995228651</v>
       </c>
       <c r="C5" s="4">
-        <v>0.5628413768458164</v>
+        <v>0.6429144995228651</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2996229947045145</v>
+        <v>0.2573758948499805</v>
       </c>
       <c r="E5" s="4">
-        <v>87.07482993197277</v>
+        <v>86.9047619047619</v>
       </c>
       <c r="F5" s="4">
-        <v>74.5662440964466</v>
+        <v>81.84563758389265</v>
       </c>
       <c r="G5" s="5">
         <v>9</v>
       </c>
       <c r="H5" s="5">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I5" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J5" s="5">
         <v>0</v>
@@ -2009,9 +2274,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.5733582118084642</v>
+      </c>
+      <c r="O5" s="5">
+        <v>9</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2867026843785794</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2867026843785794</v>
+      </c>
+      <c r="R5" s="5">
+        <v>9</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2022,6 +2305,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2029,7 +2313,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2040,9 +2324,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2076,8 +2366,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2099,75 +2397,111 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.6969224663289443</v>
+        <v>0.717473649266384</v>
       </c>
       <c r="C3" s="4">
-        <v>0.6370259271526725</v>
+        <v>0.6327272717123046</v>
       </c>
       <c r="D3" s="4">
-        <v>0.4903722864548873</v>
+        <v>0.7987990083994816</v>
       </c>
       <c r="E3" s="4">
-        <v>90.10204081632654</v>
+        <v>90.31972789115648</v>
       </c>
       <c r="F3" s="4">
-        <v>81.59731543624197</v>
+        <v>83.54809843400439</v>
       </c>
       <c r="G3" s="5">
         <v>15</v>
       </c>
       <c r="H3" s="5">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I3" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J3" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.1976979036698612</v>
+      </c>
+      <c r="O3" s="5">
+        <v>13</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.7422566760382862</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.6917381339367858</v>
+      </c>
+      <c r="R3" s="5">
+        <v>13</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4846323042866089</v>
+        <v>0.4720091069726579</v>
       </c>
       <c r="C4" s="4">
-        <v>0.4253065714540014</v>
+        <v>0.5108903683099426</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3418966656357753</v>
+        <v>0.5440246945054042</v>
       </c>
       <c r="E4" s="4">
-        <v>88.5986394557823</v>
+        <v>89</v>
       </c>
       <c r="F4" s="4">
-        <v>70.89821029082773</v>
+        <v>79.32997762863542</v>
       </c>
       <c r="G4" s="5">
         <v>10</v>
       </c>
       <c r="H4" s="5">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I4" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J4" s="5">
         <v>0</v>
@@ -2181,34 +2515,52 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.02944163986329171</v>
+      </c>
+      <c r="O4" s="5">
+        <v>9</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4720091069726579</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.5141616616280861</v>
+      </c>
+      <c r="R4" s="5">
+        <v>9</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.5881622176286151</v>
+        <v>0.776694773288543</v>
       </c>
       <c r="C5" s="4">
-        <v>0.5589731757165879</v>
+        <v>0.7509882748092119</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2347007045715372</v>
+        <v>0.3937377261818382</v>
       </c>
       <c r="E5" s="4">
-        <v>86.42857142857146</v>
+        <v>85.18518518518516</v>
       </c>
       <c r="F5" s="4">
-        <v>77.82003479989855</v>
+        <v>69.59358687546508</v>
       </c>
       <c r="G5" s="5">
         <v>9</v>
       </c>
       <c r="H5" s="5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I5" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J5" s="5">
         <v>0</v>
@@ -2222,9 +2574,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.6792075750392996</v>
+      </c>
+      <c r="O5" s="5">
+        <v>6</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.7905650001475932</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.4321898275781375</v>
+      </c>
+      <c r="R5" s="5">
+        <v>6</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2235,6 +2605,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2242,7 +2613,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2253,9 +2624,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2289,8 +2666,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2312,66 +2697,102 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>1.144517725563194</v>
+        <v>0.6954385844553315</v>
       </c>
       <c r="C3" s="4">
-        <v>0.6660654427673582</v>
+        <v>0.5733904500777892</v>
       </c>
       <c r="D3" s="4">
-        <v>0.4094177665934674</v>
+        <v>0.721273548675028</v>
       </c>
       <c r="E3" s="4">
-        <v>76.57596371882084</v>
+        <v>90.59183673469387</v>
       </c>
       <c r="F3" s="4">
-        <v>75.81804623415368</v>
+        <v>82.90454884414596</v>
       </c>
       <c r="G3" s="5">
         <v>15</v>
       </c>
       <c r="H3" s="5">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M3" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.1569225104061067</v>
+      </c>
+      <c r="O3" s="5">
+        <v>14</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.6835423627663946</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.5718532490115074</v>
+      </c>
+      <c r="R3" s="5">
+        <v>14</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.7586519131079283</v>
+        <v>0.4625028813867204</v>
       </c>
       <c r="C4" s="4">
-        <v>0.7586519131079283</v>
+        <v>0.4625028813867204</v>
       </c>
       <c r="D4" s="4">
-        <v>0.287352880291712</v>
+        <v>0.5796379452378261</v>
       </c>
       <c r="E4" s="4">
-        <v>77.95918367346938</v>
+        <v>90.87414965986395</v>
       </c>
       <c r="F4" s="4">
-        <v>79.64429530201342</v>
+        <v>84.079418344519</v>
       </c>
       <c r="G4" s="5">
         <v>10</v>
@@ -2394,50 +2815,86 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.04628124014020329</v>
+      </c>
+      <c r="O4" s="5">
+        <v>10</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4625028813867204</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.4625028813867204</v>
+      </c>
+      <c r="R4" s="5">
+        <v>10</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>1.651656102602861</v>
+        <v>0.4717097158533584</v>
       </c>
       <c r="C5" s="4">
-        <v>1.200275134758549</v>
+        <v>0.5628413768458164</v>
       </c>
       <c r="D5" s="4">
-        <v>0.6730348923040261</v>
+        <v>0.2996229947045145</v>
       </c>
       <c r="E5" s="4">
-        <v>73.86243386243393</v>
+        <v>87.07482993197277</v>
       </c>
       <c r="F5" s="4">
-        <v>68.09967685806522</v>
+        <v>74.5662440964466</v>
       </c>
       <c r="G5" s="5">
         <v>9</v>
       </c>
       <c r="H5" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I5" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J5" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.4143912597681784</v>
+      </c>
+      <c r="O5" s="5">
+        <v>7</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3696838888938582</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.4005528978954113</v>
+      </c>
+      <c r="R5" s="5">
+        <v>7</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2448,6 +2905,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2455,7 +2913,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2466,9 +2924,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2502,8 +2966,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2525,75 +2997,111 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.7364326822414661</v>
+        <v>0.6969224663289443</v>
       </c>
       <c r="C3" s="4">
-        <v>0.6111887572953004</v>
+        <v>0.6370259271526725</v>
       </c>
       <c r="D3" s="4">
-        <v>0.8208591781190552</v>
+        <v>0.4903722864548873</v>
       </c>
       <c r="E3" s="4">
-        <v>91.28344671201815</v>
+        <v>90.10204081632654</v>
       </c>
       <c r="F3" s="4">
-        <v>84.53318419090213</v>
+        <v>81.59731543624197</v>
       </c>
       <c r="G3" s="5">
         <v>15</v>
       </c>
       <c r="H3" s="5">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.006744980203566539</v>
+      </c>
+      <c r="O3" s="5">
+        <v>11</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.6991707930634665</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.6388654672081907</v>
+      </c>
+      <c r="R3" s="5">
+        <v>11</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4801035828474394</v>
+        <v>0.4846323042866089</v>
       </c>
       <c r="C4" s="4">
-        <v>0.4801035828474394</v>
+        <v>0.4253065714540014</v>
       </c>
       <c r="D4" s="4">
-        <v>0.7442739611299455</v>
+        <v>0.3418966656357753</v>
       </c>
       <c r="E4" s="4">
-        <v>90.50340136054422</v>
+        <v>88.5986394557823</v>
       </c>
       <c r="F4" s="4">
-        <v>81.09731543624159</v>
+        <v>70.89821029082773</v>
       </c>
       <c r="G4" s="5">
         <v>10</v>
       </c>
       <c r="H4" s="5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J4" s="5">
         <v>0</v>
@@ -2607,34 +3115,52 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.1817152576523792</v>
+      </c>
+      <c r="O4" s="5">
+        <v>7</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4656767095117204</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3722678278252493</v>
+      </c>
+      <c r="R4" s="5">
+        <v>7</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.3462382842423655</v>
+        <v>0.5881622176286151</v>
       </c>
       <c r="C5" s="4">
-        <v>0.3462382842423655</v>
+        <v>0.5589731757165879</v>
       </c>
       <c r="D5" s="4">
-        <v>0.527759639832095</v>
+        <v>0.2347007045715372</v>
       </c>
       <c r="E5" s="4">
-        <v>88.85865457294028</v>
+        <v>86.42857142857146</v>
       </c>
       <c r="F5" s="4">
-        <v>85.96942580164057</v>
+        <v>77.82003479989855</v>
       </c>
       <c r="G5" s="5">
         <v>9</v>
       </c>
       <c r="H5" s="5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="5">
         <v>0</v>
@@ -2648,9 +3174,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.5069914149463131</v>
+      </c>
+      <c r="O5" s="5">
+        <v>8</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.468470124433624</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3609456440039338</v>
+      </c>
+      <c r="R5" s="5">
+        <v>8</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2661,6 +3205,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2668,7 +3213,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2679,9 +3224,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2715,8 +3266,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2738,132 +3297,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>1.05439249834904</v>
+        <v>1.144517725563194</v>
       </c>
       <c r="C3" s="4">
-        <v>0.7142360656257312</v>
+        <v>0.6660654427673582</v>
       </c>
       <c r="D3" s="4">
-        <v>0.4421095721113014</v>
+        <v>0.4094177665934674</v>
       </c>
       <c r="E3" s="4">
-        <v>62.35374149659864</v>
+        <v>76.57596371882084</v>
       </c>
       <c r="F3" s="4">
-        <v>69.12378821774745</v>
+        <v>75.81804623415368</v>
       </c>
       <c r="G3" s="5">
         <v>15</v>
       </c>
       <c r="H3" s="5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>2</v>
+      </c>
+      <c r="N3" s="4">
+        <v>1.027464642362869</v>
+      </c>
+      <c r="O3" s="5">
+        <v>10</v>
+      </c>
+      <c r="P3" s="4">
+        <v>1.188838738041853</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.6506935437994595</v>
+      </c>
+      <c r="R3" s="5">
+        <v>10</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.825943983496745</v>
+        <v>0.7586519131079283</v>
       </c>
       <c r="C4" s="4">
-        <v>0.8980917123866634</v>
+        <v>0.7586519131079283</v>
       </c>
       <c r="D4" s="4">
-        <v>0.4427151954325607</v>
+        <v>0.287352880291712</v>
       </c>
       <c r="E4" s="4">
-        <v>61.94897959183673</v>
+        <v>77.95918367346938</v>
       </c>
       <c r="F4" s="4">
-        <v>74.74832214765101</v>
+        <v>79.64429530201342</v>
       </c>
       <c r="G4" s="5">
         <v>10</v>
       </c>
       <c r="H4" s="5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.7316787667620472</v>
+      </c>
+      <c r="O4" s="5">
+        <v>10</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4717756475000899</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.4717756475000899</v>
+      </c>
+      <c r="R4" s="5">
+        <v>10</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>1.475369885944823</v>
+        <v>1.651656102602861</v>
       </c>
       <c r="C5" s="4">
-        <v>0.6877682048561459</v>
+        <v>1.200275134758549</v>
       </c>
       <c r="D5" s="4">
-        <v>0.707529192987416</v>
+        <v>0.6730348923040261</v>
       </c>
       <c r="E5" s="4">
-        <v>54.38775510204103</v>
+        <v>73.86243386243393</v>
       </c>
       <c r="F5" s="4">
-        <v>60.06711409395925</v>
+        <v>68.09967685806522</v>
       </c>
       <c r="G5" s="5">
         <v>9</v>
       </c>
       <c r="H5" s="5">
+        <v>6</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
         <v>3</v>
       </c>
-      <c r="I5" s="5">
-        <v>1</v>
-      </c>
-      <c r="J5" s="5">
-        <v>5</v>
-      </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>1.200275134758549</v>
+      </c>
+      <c r="O5" s="5">
+        <v>6</v>
+      </c>
+      <c r="P5" s="4">
+        <v>1.532658712206701</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.4216414817850327</v>
+      </c>
+      <c r="R5" s="5">
+        <v>6</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2874,6 +3505,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2881,7 +3513,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2892,9 +3524,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2928,8 +3566,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2951,34 +3597,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.7206893670216021</v>
+        <v>0.7364326822414661</v>
       </c>
       <c r="C3" s="4">
-        <v>0.6622053046140786</v>
+        <v>0.6111887572953004</v>
       </c>
       <c r="D3" s="4">
-        <v>0.9373186312248907</v>
+        <v>0.8208591781190552</v>
       </c>
       <c r="E3" s="4">
-        <v>90.44217687074831</v>
+        <v>91.28344671201815</v>
       </c>
       <c r="F3" s="4">
-        <v>81.44519015659968</v>
+        <v>84.53318419090213</v>
       </c>
       <c r="G3" s="5">
         <v>15</v>
       </c>
       <c r="H3" s="5">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I3" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J3" s="5">
         <v>1</v>
@@ -2992,34 +3656,52 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.2294774868872259</v>
+      </c>
+      <c r="O3" s="5">
+        <v>13</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.6478892023122508</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.5443274322827021</v>
+      </c>
+      <c r="R3" s="5">
+        <v>13</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4616142995240605</v>
+        <v>0.4801035828474394</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3887538529759141</v>
+        <v>0.4801035828474394</v>
       </c>
       <c r="D4" s="4">
-        <v>0.6880995398193956</v>
+        <v>0.7442739611299455</v>
       </c>
       <c r="E4" s="4">
-        <v>89.61224489795919</v>
+        <v>90.50340136054422</v>
       </c>
       <c r="F4" s="4">
-        <v>77.34675615212439</v>
+        <v>81.09731543624159</v>
       </c>
       <c r="G4" s="5">
         <v>10</v>
       </c>
       <c r="H4" s="5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" s="5">
         <v>0</v>
@@ -3033,25 +3715,43 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.2157702498091137</v>
+      </c>
+      <c r="O4" s="5">
+        <v>10</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4369495328856166</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.4369495328856166</v>
+      </c>
+      <c r="R4" s="5">
+        <v>10</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.3037270183664447</v>
+        <v>0.3462382842423655</v>
       </c>
       <c r="C5" s="4">
-        <v>0.3037270183664447</v>
+        <v>0.3462382842423655</v>
       </c>
       <c r="D5" s="4">
-        <v>0.4204095950519391</v>
+        <v>0.527759639832095</v>
       </c>
       <c r="E5" s="4">
-        <v>88.23885109599395</v>
+        <v>88.85865457294028</v>
       </c>
       <c r="F5" s="4">
-        <v>83.92493164305253</v>
+        <v>85.96942580164057</v>
       </c>
       <c r="G5" s="5">
         <v>9</v>
@@ -3074,9 +3774,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.06556628562684984</v>
+      </c>
+      <c r="O5" s="5">
+        <v>9</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3359400808235408</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3359400808235408</v>
+      </c>
+      <c r="R5" s="5">
+        <v>9</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3087,12 +3805,1468 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>1.05439249834904</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.7142360656257312</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.4421095721113014</v>
+      </c>
+      <c r="E3" s="4">
+        <v>62.35374149659864</v>
+      </c>
+      <c r="F3" s="4">
+        <v>69.12378821774745</v>
+      </c>
+      <c r="G3" s="5">
+        <v>15</v>
+      </c>
+      <c r="H3" s="5">
+        <v>6</v>
+      </c>
+      <c r="I3" s="5">
+        <v>1</v>
+      </c>
+      <c r="J3" s="5">
+        <v>8</v>
+      </c>
+      <c r="K3" s="5">
+        <v>1</v>
+      </c>
+      <c r="L3" s="5">
+        <v>7</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.7142360656257312</v>
+      </c>
+      <c r="O3" s="5">
+        <v>6</v>
+      </c>
+      <c r="P3" s="4">
+        <v>1.016215961431193</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3003772461047207</v>
+      </c>
+      <c r="R3" s="5">
+        <v>6</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.825943983496745</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.8980917123866634</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.4427151954325607</v>
+      </c>
+      <c r="E4" s="4">
+        <v>61.94897959183673</v>
+      </c>
+      <c r="F4" s="4">
+        <v>74.74832214765101</v>
+      </c>
+      <c r="G4" s="5">
+        <v>10</v>
+      </c>
+      <c r="H4" s="5">
+        <v>6</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>4</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>4</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.6909218912787572</v>
+      </c>
+      <c r="O4" s="5">
+        <v>6</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.468692564235475</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.4772503658937495</v>
+      </c>
+      <c r="R4" s="5">
+        <v>6</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>1.475369885944823</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.6877682048561459</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.707529192987416</v>
+      </c>
+      <c r="E5" s="4">
+        <v>54.38775510204103</v>
+      </c>
+      <c r="F5" s="4">
+        <v>60.06711409395925</v>
+      </c>
+      <c r="G5" s="5">
+        <v>9</v>
+      </c>
+      <c r="H5" s="5">
+        <v>3</v>
+      </c>
+      <c r="I5" s="5">
+        <v>1</v>
+      </c>
+      <c r="J5" s="5">
+        <v>5</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>5</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>3</v>
+      </c>
+      <c r="P5" s="4">
+        <v>1.475369885944823</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.6877682048561459</v>
+      </c>
+      <c r="R5" s="5">
+        <v>3</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.7206893670216021</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.6622053046140786</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.9373186312248907</v>
+      </c>
+      <c r="E3" s="4">
+        <v>90.44217687074831</v>
+      </c>
+      <c r="F3" s="4">
+        <v>81.44519015659968</v>
+      </c>
+      <c r="G3" s="5">
+        <v>15</v>
+      </c>
+      <c r="H3" s="5">
+        <v>11</v>
+      </c>
+      <c r="I3" s="5">
+        <v>3</v>
+      </c>
+      <c r="J3" s="5">
+        <v>1</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>1</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.396815333107944</v>
+      </c>
+      <c r="O3" s="5">
+        <v>11</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.6031139359871855</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.5712524270989939</v>
+      </c>
+      <c r="R3" s="5">
+        <v>11</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.4616142995240605</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.3887538529759141</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.6880995398193956</v>
+      </c>
+      <c r="E4" s="4">
+        <v>89.61224489795919</v>
+      </c>
+      <c r="F4" s="4">
+        <v>77.34675615212439</v>
+      </c>
+      <c r="G4" s="5">
+        <v>10</v>
+      </c>
+      <c r="H4" s="5">
+        <v>9</v>
+      </c>
+      <c r="I4" s="5">
+        <v>1</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.1928212624944033</v>
+      </c>
+      <c r="O4" s="5">
+        <v>9</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4558833193630359</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3609615125198421</v>
+      </c>
+      <c r="R4" s="5">
+        <v>9</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.3037270183664447</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.3037270183664447</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.4204095950519391</v>
+      </c>
+      <c r="E5" s="4">
+        <v>88.23885109599395</v>
+      </c>
+      <c r="F5" s="4">
+        <v>83.92493164305253</v>
+      </c>
+      <c r="G5" s="5">
+        <v>9</v>
+      </c>
+      <c r="H5" s="5">
+        <v>9</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>0.07250149629827579</v>
+      </c>
+      <c r="O5" s="5">
+        <v>9</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2900492263587944</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2900492263587944</v>
+      </c>
+      <c r="R5" s="5">
+        <v>9</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>82.35294117647058</v>
+      </c>
+      <c r="C3" s="3">
+        <v>14.70588235294118</v>
+      </c>
+      <c r="D3" s="3">
+        <v>2.941176470588235</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3">
+        <v>2.941176470588235</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.6316853652735562</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.5284559359178584</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0.5029850246453006</v>
+      </c>
+      <c r="K3" s="4">
+        <v>85.95938375350147</v>
+      </c>
+      <c r="L3" s="4">
+        <v>79.67989209106516</v>
+      </c>
+      <c r="M3" s="5">
+        <v>34</v>
+      </c>
+      <c r="N3" s="5">
+        <v>228791.5854454041</v>
+      </c>
+      <c r="O3" s="4">
+        <v>37.74193095437217</v>
+      </c>
+      <c r="P3" s="5">
+        <v>6062</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>79.41176470588235</v>
+      </c>
+      <c r="C4" s="3">
+        <v>8.823529411764707</v>
+      </c>
+      <c r="D4" s="3">
+        <v>11.76470588235294</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>2.941176470588235</v>
+      </c>
+      <c r="G4" s="3">
+        <v>8.823529411764707</v>
+      </c>
+      <c r="H4" s="4">
+        <v>1.336142792843694</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.6792419459640576</v>
+      </c>
+      <c r="J4" s="4">
+        <v>1.24986181517939</v>
+      </c>
+      <c r="K4" s="4">
+        <v>87.71508603441376</v>
+      </c>
+      <c r="L4" s="4">
+        <v>82.85366495591533</v>
+      </c>
+      <c r="M4" s="5">
+        <v>34</v>
+      </c>
+      <c r="N4" s="5">
+        <v>626919.0261363983</v>
+      </c>
+      <c r="O4" s="4">
+        <v>109.8508894579286</v>
+      </c>
+      <c r="P4" s="5">
+        <v>5707</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>85.29411764705883</v>
+      </c>
+      <c r="C5" s="3">
+        <v>11.76470588235294</v>
+      </c>
+      <c r="D5" s="3">
+        <v>2.941176470588235</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>2.941176470588235</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.5097155717600752</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.4792968434351944</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0.6982753462454127</v>
+      </c>
+      <c r="K5" s="4">
+        <v>89.47478991596641</v>
+      </c>
+      <c r="L5" s="4">
+        <v>83.10929069614154</v>
+      </c>
+      <c r="M5" s="5">
+        <v>34</v>
+      </c>
+      <c r="N5" s="5">
+        <v>685485.7110977173</v>
+      </c>
+      <c r="O5" s="4">
+        <v>160.0480296749282</v>
+      </c>
+      <c r="P5" s="5">
+        <v>4283</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>91.17647058823529</v>
+      </c>
+      <c r="C6" s="3">
+        <v>5.88235294117647</v>
+      </c>
+      <c r="D6" s="3">
+        <v>2.941176470588235</v>
+      </c>
+      <c r="E6" s="3">
+        <v>2.941176470588235</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.4953361143870802</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.5190673547604633</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.5748498570197437</v>
+      </c>
+      <c r="K6" s="4">
+        <v>88.97859143657466</v>
+      </c>
+      <c r="L6" s="4">
+        <v>80.49940781681819</v>
+      </c>
+      <c r="M6" s="5">
+        <v>34</v>
+      </c>
+      <c r="N6" s="5">
+        <v>766927.5109767914</v>
+      </c>
+      <c r="O6" s="4">
+        <v>107.262588947803</v>
+      </c>
+      <c r="P6" s="5">
+        <v>7150</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>91.17647058823529</v>
+      </c>
+      <c r="C7" s="3">
+        <v>2.941176470588235</v>
+      </c>
+      <c r="D7" s="3">
+        <v>5.88235294117647</v>
+      </c>
+      <c r="E7" s="3">
+        <v>2.941176470588235</v>
+      </c>
+      <c r="F7" s="3">
+        <v>2.941176470588235</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.541193945096494</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.4665699937087399</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.5307000940482965</v>
+      </c>
+      <c r="K7" s="4">
+        <v>91.35454181672678</v>
+      </c>
+      <c r="L7" s="4">
+        <v>84.92926700881412</v>
+      </c>
+      <c r="M7" s="5">
+        <v>34</v>
+      </c>
+      <c r="N7" s="5">
+        <v>2260681.818246841</v>
+      </c>
+      <c r="O7" s="4">
+        <v>525.2513518231509</v>
+      </c>
+      <c r="P7" s="5">
+        <v>4304</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>91.17647058823529</v>
+      </c>
+      <c r="C8" s="3">
+        <v>5.88235294117647</v>
+      </c>
+      <c r="D8" s="3">
+        <v>2.941176470588235</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>2.941176470588235</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.7368940773822578</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.7194753021592244</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.499880338074898</v>
+      </c>
+      <c r="K8" s="4">
+        <v>88.50240096038416</v>
+      </c>
+      <c r="L8" s="4">
+        <v>81.72325305961169</v>
+      </c>
+      <c r="M8" s="5">
+        <v>34</v>
+      </c>
+      <c r="N8" s="5">
+        <v>155855.9422492981</v>
+      </c>
+      <c r="O8" s="4">
+        <v>31.89194643938983</v>
+      </c>
+      <c r="P8" s="5">
+        <v>4887</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>85.29411764705883</v>
+      </c>
+      <c r="C9" s="3">
+        <v>8.823529411764707</v>
+      </c>
+      <c r="D9" s="3">
+        <v>5.88235294117647</v>
+      </c>
+      <c r="E9" s="3">
+        <v>2.941176470588235</v>
+      </c>
+      <c r="F9" s="3">
+        <v>2.941176470588235</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.7813205247978028</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.7844396291406315</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.5364347048708735</v>
+      </c>
+      <c r="K9" s="4">
+        <v>86.38455382152864</v>
+      </c>
+      <c r="L9" s="4">
+        <v>81.48703776812648</v>
+      </c>
+      <c r="M9" s="5">
+        <v>34</v>
+      </c>
+      <c r="N9" s="5">
+        <v>217279.2935371399</v>
+      </c>
+      <c r="O9" s="4">
+        <v>41.03480520059299</v>
+      </c>
+      <c r="P9" s="5">
+        <v>5295</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>88.23529411764706</v>
+      </c>
+      <c r="C10" s="3">
+        <v>8.823529411764707</v>
+      </c>
+      <c r="D10" s="3">
+        <v>2.941176470588235</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>2.941176470588235</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.4496667628891226</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.4040840164208224</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.6088899968444013</v>
+      </c>
+      <c r="K10" s="4">
+        <v>88.99659863945577</v>
+      </c>
+      <c r="L10" s="4">
+        <v>82.29701276483758</v>
+      </c>
+      <c r="M10" s="5">
+        <v>34</v>
+      </c>
+      <c r="N10" s="5">
+        <v>452072.8783607483</v>
+      </c>
+      <c r="O10" s="4">
+        <v>82.84274846266231</v>
+      </c>
+      <c r="P10" s="5">
+        <v>5457</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>82.35294117647058</v>
+      </c>
+      <c r="C11" s="3">
+        <v>14.70588235294118</v>
+      </c>
+      <c r="D11" s="3">
+        <v>2.941176470588235</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3">
+        <v>2.941176470588235</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.6755595944596827</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.5790424879035648</v>
+      </c>
+      <c r="J11" s="4">
+        <v>0.5757376061068264</v>
+      </c>
+      <c r="K11" s="4">
+        <v>88.57242897158864</v>
+      </c>
+      <c r="L11" s="4">
+        <v>78.61363337281141</v>
+      </c>
+      <c r="M11" s="5">
+        <v>34</v>
+      </c>
+      <c r="N11" s="5">
+        <v>281107.3083877563</v>
+      </c>
+      <c r="O11" s="4">
+        <v>51.62668657259069</v>
+      </c>
+      <c r="P11" s="5">
+        <v>5445</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>91.17647058823529</v>
+      </c>
+      <c r="C12" s="3">
+        <v>5.88235294117647</v>
+      </c>
+      <c r="D12" s="3">
+        <v>2.941176470588235</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3">
+        <v>2.941176470588235</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.5354505663355249</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.4978982124289092</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0.5799111514753003</v>
+      </c>
+      <c r="K12" s="4">
+        <v>89.74389755902361</v>
+      </c>
+      <c r="L12" s="4">
+        <v>81.04290038162958</v>
+      </c>
+      <c r="M12" s="5">
+        <v>34</v>
+      </c>
+      <c r="N12" s="5">
+        <v>153809.5681667328</v>
+      </c>
+      <c r="O12" s="4">
+        <v>30.96629115496936</v>
+      </c>
+      <c r="P12" s="5">
+        <v>4967</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>76.47058823529412</v>
+      </c>
+      <c r="C13" s="3">
+        <v>17.64705882352941</v>
+      </c>
+      <c r="D13" s="3">
+        <v>5.88235294117647</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3">
+        <v>5.88235294117647</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.5694282385579946</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.4815753879268582</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0.4612517947135663</v>
+      </c>
+      <c r="K13" s="4">
+        <v>88.68747498999606</v>
+      </c>
+      <c r="L13" s="4">
+        <v>77.45065140150128</v>
+      </c>
+      <c r="M13" s="5">
+        <v>34</v>
+      </c>
+      <c r="N13" s="5">
+        <v>389855.1921844482</v>
+      </c>
+      <c r="O13" s="4">
+        <v>76.54725941182961</v>
+      </c>
+      <c r="P13" s="5">
+        <v>5093</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>76.47058823529412</v>
+      </c>
+      <c r="C14" s="3">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3">
+        <v>23.52941176470588</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>23.52941176470588</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <v>1.068948998690853</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.5290208001425266</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.6788024219311323</v>
+      </c>
+      <c r="K14" s="4">
+        <v>76.26450580232097</v>
+      </c>
+      <c r="L14" s="4">
+        <v>74.90031583103136</v>
+      </c>
+      <c r="M14" s="5">
+        <v>34</v>
+      </c>
+      <c r="N14" s="5">
+        <v>5502865.86022377</v>
+      </c>
+      <c r="O14" s="4">
+        <v>687.514475290326</v>
+      </c>
+      <c r="P14" s="5">
+        <v>8004</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>94.11764705882352</v>
+      </c>
+      <c r="C15" s="3">
+        <v>2.941176470588235</v>
+      </c>
+      <c r="D15" s="3">
+        <v>2.941176470588235</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>2.941176470588235</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.5032733556162292</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.4521628961232237</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.5842711163248419</v>
+      </c>
+      <c r="K15" s="4">
+        <v>90.41216486594638</v>
+      </c>
+      <c r="L15" s="4">
+        <v>83.90281616002076</v>
+      </c>
+      <c r="M15" s="5">
+        <v>34</v>
+      </c>
+      <c r="N15" s="5">
+        <v>3721835.453987122</v>
+      </c>
+      <c r="O15" s="4">
+        <v>738.8992364477112</v>
+      </c>
+      <c r="P15" s="5">
+        <v>5037</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>44.11764705882353</v>
+      </c>
+      <c r="C16" s="3">
+        <v>5.88235294117647</v>
+      </c>
+      <c r="D16" s="3">
+        <v>50</v>
+      </c>
+      <c r="E16" s="3">
+        <v>2.941176470588235</v>
+      </c>
+      <c r="F16" s="3">
+        <v>47.05882352941176</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.9767204128625309</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.4486046857706174</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0.6718133340614711</v>
+      </c>
+      <c r="K16" s="4">
+        <v>60.12605042016826</v>
+      </c>
+      <c r="L16" s="4">
+        <v>68.3807079878916</v>
+      </c>
+      <c r="M16" s="5">
+        <v>34</v>
+      </c>
+      <c r="N16" s="5">
+        <v>1134688.172340393</v>
+      </c>
+      <c r="O16" s="4">
+        <v>129.3239311990419</v>
+      </c>
+      <c r="P16" s="5">
+        <v>8774</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3">
+        <v>85.29411764705883</v>
+      </c>
+      <c r="C17" s="3">
+        <v>11.76470588235294</v>
+      </c>
+      <c r="D17" s="3">
+        <v>2.941176470588235</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>2.941176470588235</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0.4769407432549204</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.4187197706205745</v>
+      </c>
+      <c r="J17" s="4">
+        <v>0.5966526322034327</v>
+      </c>
+      <c r="K17" s="4">
+        <v>89.61484593837534</v>
+      </c>
+      <c r="L17" s="4">
+        <v>80.89617054875573</v>
+      </c>
+      <c r="M17" s="5">
+        <v>34</v>
+      </c>
+      <c r="N17" s="5">
+        <v>639078.8025856018</v>
+      </c>
+      <c r="O17" s="4">
+        <v>135.9742133160855</v>
+      </c>
+      <c r="P17" s="5">
+        <v>4700</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3338,7 +5512,7 @@
         <v>0</v>
       </c>
       <c r="K6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" s="5">
         <v>0</v>
@@ -3781,13 +5955,13 @@
         <v>0</v>
       </c>
       <c r="L16" s="5">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M16" s="5">
         <v>0</v>
       </c>
       <c r="N16" s="5">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="25" customHeight="1">
@@ -3847,9 +6021,764 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>28</v>
+      </c>
+      <c r="C3" s="5">
+        <v>5</v>
+      </c>
+      <c r="D3" s="5">
+        <v>1</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0</v>
+      </c>
+      <c r="F3" s="5">
+        <v>1</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>1</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>27</v>
+      </c>
+      <c r="C4" s="5">
+        <v>3</v>
+      </c>
+      <c r="D4" s="5">
+        <v>4</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5">
+        <v>1</v>
+      </c>
+      <c r="G4" s="5">
+        <v>3</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>1</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>29</v>
+      </c>
+      <c r="C5" s="5">
+        <v>4</v>
+      </c>
+      <c r="D5" s="5">
+        <v>1</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5">
+        <v>1</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>1</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>31</v>
+      </c>
+      <c r="C6" s="5">
+        <v>2</v>
+      </c>
+      <c r="D6" s="5">
+        <v>1</v>
+      </c>
+      <c r="E6" s="5">
+        <v>1</v>
+      </c>
+      <c r="F6" s="5">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>1</v>
+      </c>
+      <c r="I6" s="5">
+        <v>1</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>0</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>31</v>
+      </c>
+      <c r="C7" s="5">
+        <v>1</v>
+      </c>
+      <c r="D7" s="5">
+        <v>2</v>
+      </c>
+      <c r="E7" s="5">
+        <v>1</v>
+      </c>
+      <c r="F7" s="5">
+        <v>1</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>1</v>
+      </c>
+      <c r="I7" s="5">
+        <v>1</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>1</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>31</v>
+      </c>
+      <c r="C8" s="5">
+        <v>2</v>
+      </c>
+      <c r="D8" s="5">
+        <v>1</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>1</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>1</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>29</v>
+      </c>
+      <c r="C9" s="5">
+        <v>3</v>
+      </c>
+      <c r="D9" s="5">
+        <v>2</v>
+      </c>
+      <c r="E9" s="5">
+        <v>1</v>
+      </c>
+      <c r="F9" s="5">
+        <v>1</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
+        <v>1</v>
+      </c>
+      <c r="I9" s="5">
+        <v>1</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>1</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>30</v>
+      </c>
+      <c r="C10" s="5">
+        <v>3</v>
+      </c>
+      <c r="D10" s="5">
+        <v>1</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5">
+        <v>1</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>1</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>28</v>
+      </c>
+      <c r="C11" s="5">
+        <v>5</v>
+      </c>
+      <c r="D11" s="5">
+        <v>1</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5">
+        <v>1</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>1</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>31</v>
+      </c>
+      <c r="C12" s="5">
+        <v>2</v>
+      </c>
+      <c r="D12" s="5">
+        <v>1</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5">
+        <v>1</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>1</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>26</v>
+      </c>
+      <c r="C13" s="5">
+        <v>6</v>
+      </c>
+      <c r="D13" s="5">
+        <v>2</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5">
+        <v>2</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5">
+        <v>2</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>26</v>
+      </c>
+      <c r="C14" s="5">
+        <v>0</v>
+      </c>
+      <c r="D14" s="5">
+        <v>8</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5">
+        <v>8</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <v>8</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>32</v>
+      </c>
+      <c r="C15" s="5">
+        <v>1</v>
+      </c>
+      <c r="D15" s="5">
+        <v>1</v>
+      </c>
+      <c r="E15" s="5">
+        <v>0</v>
+      </c>
+      <c r="F15" s="5">
+        <v>1</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <v>1</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>15</v>
+      </c>
+      <c r="C16" s="5">
+        <v>2</v>
+      </c>
+      <c r="D16" s="5">
+        <v>17</v>
+      </c>
+      <c r="E16" s="5">
+        <v>1</v>
+      </c>
+      <c r="F16" s="5">
+        <v>16</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>1</v>
+      </c>
+      <c r="I16" s="5">
+        <v>1</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>14</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5">
+        <v>29</v>
+      </c>
+      <c r="C17" s="5">
+        <v>4</v>
+      </c>
+      <c r="D17" s="5">
+        <v>1</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5">
+        <v>1</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>1</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3860,9 +6789,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3896,8 +6831,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3919,10 +6862,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.6912404658701405</v>
@@ -3960,10 +6921,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.00934706011847714</v>
+      </c>
+      <c r="O3" s="5">
+        <v>11</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.6906173285289087</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.6850728163029828</v>
+      </c>
+      <c r="R3" s="5">
+        <v>11</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.4972304373737672</v>
@@ -4001,10 +6980,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.1715155102360285</v>
+      </c>
+      <c r="O4" s="5">
+        <v>10</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4801664556054702</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.4801664556054702</v>
+      </c>
+      <c r="R4" s="5">
+        <v>10</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.8852198712398578</v>
@@ -4042,9 +7039,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.8016823846570073</v>
+      </c>
+      <c r="O5" s="5">
+        <v>7</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.7018197705902868</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3513286671875031</v>
+      </c>
+      <c r="R5" s="5">
+        <v>7</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4055,14 +7070,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4073,9 +7089,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4109,8 +7131,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4132,10 +7162,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>2.397798074969435</v>
@@ -4173,10 +7221,28 @@
       <c r="M3" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.6682889997292679</v>
+      </c>
+      <c r="O3" s="5">
+        <v>11</v>
+      </c>
+      <c r="P3" s="4">
+        <v>2.351328011243043</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>1.022574719123698</v>
+      </c>
+      <c r="R3" s="5">
+        <v>8</v>
+      </c>
+      <c r="S3" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.6356477941064469</v>
@@ -4214,17 +7280,33 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.02776903883099919</v>
+      </c>
+      <c r="O4" s="5">
+        <v>10</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.6403178215914045</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.6403178215914045</v>
+      </c>
+      <c r="R4" s="5">
+        <v>10</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>4.605200028243833</v>
       </c>
-      <c r="C5" s="4">
-        <v>0</v>
-      </c>
+      <c r="C5" s="4"/>
       <c r="D5" s="4">
         <v>4.354437194754521</v>
       </c>
@@ -4255,9 +7337,27 @@
       <c r="M5" s="5">
         <v>9</v>
       </c>
+      <c r="N5" s="4">
+        <v>4.605200028243833</v>
+      </c>
+      <c r="O5" s="5">
+        <v>9</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4173062857917691</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.4173062857917691</v>
+      </c>
+      <c r="R5" s="5">
+        <v>9</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4268,14 +7368,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4286,9 +7387,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4322,8 +7429,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4345,10 +7460,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.6511445151682457</v>
@@ -4386,10 +7519,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.338493848320026</v>
+      </c>
+      <c r="O3" s="5">
+        <v>11</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.6113763410993092</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.5398848584149571</v>
+      </c>
+      <c r="R3" s="5">
+        <v>11</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.4194812600166216</v>
@@ -4427,10 +7578,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.02905986457585925</v>
+      </c>
+      <c r="O4" s="5">
+        <v>10</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4194812600166216</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.4194812600166216</v>
+      </c>
+      <c r="R4" s="5">
+        <v>10</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.5369586679242704</v>
@@ -4468,9 +7637,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.3013663586571766</v>
+      </c>
+      <c r="O5" s="5">
+        <v>8</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4405413025763004</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.4707578021112369</v>
+      </c>
+      <c r="R5" s="5">
+        <v>8</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4481,14 +7668,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4499,9 +7687,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4535,8 +7729,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4558,10 +7760,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.6059159732746916</v>
@@ -4599,10 +7819,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.02991345979129838</v>
+      </c>
+      <c r="O3" s="5">
+        <v>14</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.599933281316432</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.6286416351423271</v>
+      </c>
+      <c r="R3" s="5">
+        <v>14</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.5066076785084107</v>
@@ -4640,10 +7878,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.2142406898315604</v>
+      </c>
+      <c r="O4" s="5">
+        <v>9</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4947904790429704</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.4942234605507292</v>
+      </c>
+      <c r="R4" s="5">
+        <v>9</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.6776469429433468</v>
@@ -4681,9 +7937,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.615856914442773</v>
+      </c>
+      <c r="O5" s="5">
+        <v>8</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3216137643316159</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3552617450781526</v>
+      </c>
+      <c r="R5" s="5">
+        <v>8</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4694,14 +7968,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4712,9 +7987,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4748,8 +8029,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4771,10 +8060,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.667537478373714</v>
@@ -4812,10 +8119,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.07028798992642202</v>
+      </c>
+      <c r="O3" s="5">
+        <v>13</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.6880071724976186</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.56892013660413</v>
+      </c>
+      <c r="R3" s="5">
+        <v>13</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.4303889371040014</v>
@@ -4853,10 +8178,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.123158023511175</v>
+      </c>
+      <c r="O4" s="5">
+        <v>10</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4550205418062364</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.4550205418062364</v>
+      </c>
+      <c r="R4" s="5">
+        <v>10</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.5120780801890987</v>
@@ -4894,9 +8237,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.4841041850268795</v>
+      </c>
+      <c r="O5" s="5">
+        <v>8</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3922534586393501</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.31468782638186</v>
+      </c>
+      <c r="R5" s="5">
+        <v>8</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4907,432 +8268,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.9889725316759489</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.6077639389531091</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.8355656296946063</v>
-      </c>
-      <c r="E3" s="4">
-        <v>89.23809523809523</v>
-      </c>
-      <c r="F3" s="4">
-        <v>82.24161073825488</v>
-      </c>
-      <c r="G3" s="5">
-        <v>15</v>
-      </c>
-      <c r="H3" s="5">
-        <v>10</v>
-      </c>
-      <c r="I3" s="5">
-        <v>1</v>
-      </c>
-      <c r="J3" s="5">
-        <v>4</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>1</v>
-      </c>
-      <c r="M3" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.6878769108145679</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.6710727535371608</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.5899931000737741</v>
-      </c>
-      <c r="E4" s="4">
-        <v>88.62244897959184</v>
-      </c>
-      <c r="F4" s="4">
-        <v>79.19463087248322</v>
-      </c>
-      <c r="G4" s="5">
-        <v>10</v>
-      </c>
-      <c r="H4" s="5">
-        <v>9</v>
-      </c>
-      <c r="I4" s="5">
-        <v>1</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.5433500928570432</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.5433500928570432</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.452993599078237</v>
-      </c>
-      <c r="E5" s="4">
-        <v>87.14285714285714</v>
-      </c>
-      <c r="F5" s="4">
-        <v>83.668903803132</v>
-      </c>
-      <c r="G5" s="5">
-        <v>9</v>
-      </c>
-      <c r="H5" s="5">
-        <v>9</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>1.021245510080191</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.9344672499660689</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.7421182182424388</v>
-      </c>
-      <c r="E3" s="4">
-        <v>87.36734693877551</v>
-      </c>
-      <c r="F3" s="4">
-        <v>82.86577181208038</v>
-      </c>
-      <c r="G3" s="5">
-        <v>15</v>
-      </c>
-      <c r="H3" s="5">
-        <v>12</v>
-      </c>
-      <c r="I3" s="5">
-        <v>1</v>
-      </c>
-      <c r="J3" s="5">
-        <v>2</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>1</v>
-      </c>
-      <c r="M3" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.7168151479347017</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.7168151479347017</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.6354155164344576</v>
-      </c>
-      <c r="E4" s="4">
-        <v>87.68367346938776</v>
-      </c>
-      <c r="F4" s="4">
-        <v>87.11409395973155</v>
-      </c>
-      <c r="G4" s="5">
-        <v>10</v>
-      </c>
-      <c r="H4" s="5">
-        <v>10</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.6868712014722733</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.8787955741052732</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.7026666824915411</v>
-      </c>
-      <c r="E5" s="4">
-        <v>83.30309901738471</v>
-      </c>
-      <c r="F5" s="4">
-        <v>72.93686303753378</v>
-      </c>
-      <c r="G5" s="5">
-        <v>9</v>
-      </c>
-      <c r="H5" s="5">
-        <v>6</v>
-      </c>
-      <c r="I5" s="5">
-        <v>2</v>
-      </c>
-      <c r="J5" s="5">
-        <v>1</v>
-      </c>
-      <c r="K5" s="5">
-        <v>1</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/downloads/SarkerPrediction2023.xlsx
+++ b/public/downloads/SarkerPrediction2023.xlsx
@@ -1557,22 +1557,22 @@
         <v>3</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.5305578991571226</v>
+        <v>0.07398418918637617</v>
       </c>
       <c r="O3" s="5">
         <v>13</v>
       </c>
       <c r="P3" s="4">
-        <v>1.017571473039275</v>
+        <v>0.9939048109550407</v>
       </c>
       <c r="Q3" s="4">
-        <v>1.017008309910844</v>
+        <v>0.5781702632785587</v>
       </c>
       <c r="R3" s="5">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="S3" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -1616,16 +1616,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.130914128998574</v>
+        <v>-0.2864953486562172</v>
       </c>
       <c r="O4" s="5">
         <v>9</v>
       </c>
       <c r="P4" s="4">
-        <v>0.6616940850148531</v>
+        <v>0.6305778410833245</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.6565267392039859</v>
+        <v>0.6392399370198033</v>
       </c>
       <c r="R4" s="5">
         <v>9</v>
@@ -1675,16 +1675,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.4622175358743278</v>
+        <v>0.3965048346154845</v>
       </c>
       <c r="O5" s="5">
         <v>9</v>
       </c>
       <c r="P5" s="4">
-        <v>0.3526539650287899</v>
+        <v>0.3453525537778073</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.3526539650287899</v>
+        <v>0.3453525537778073</v>
       </c>
       <c r="R5" s="5">
         <v>9</v>
@@ -1857,22 +1857,22 @@
         <v>1</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3496225510211253</v>
+        <v>0.1476074833899474</v>
       </c>
       <c r="O3" s="5">
         <v>13</v>
       </c>
       <c r="P3" s="4">
-        <v>1.044553680148266</v>
+        <v>1.023495891458365</v>
       </c>
       <c r="Q3" s="4">
-        <v>1.051402389077328</v>
+        <v>0.679195909843773</v>
       </c>
       <c r="R3" s="5">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="S3" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -1916,16 +1916,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1939627669703924</v>
+        <v>-0.4469719110992969</v>
       </c>
       <c r="O4" s="5">
         <v>10</v>
       </c>
       <c r="P4" s="4">
-        <v>0.6780225945406231</v>
+        <v>0.6522855962304703</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.6780225945406231</v>
+        <v>0.6522855962304703</v>
       </c>
       <c r="R4" s="5">
         <v>10</v>
@@ -1975,16 +1975,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.8585792498948498</v>
+        <v>1.001421070962579</v>
       </c>
       <c r="O5" s="5">
         <v>6</v>
       </c>
       <c r="P5" s="4">
-        <v>0.457374077277231</v>
+        <v>0.4853435650694817</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.3833820402778024</v>
+        <v>0.3539153614323141</v>
       </c>
       <c r="R5" s="5">
         <v>6</v>
@@ -2157,16 +2157,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.01756953263081843</v>
+        <v>-0.1115394028396395</v>
       </c>
       <c r="O3" s="5">
         <v>11</v>
       </c>
       <c r="P3" s="4">
-        <v>0.5701628704157689</v>
+        <v>0.5513688963740047</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.4896630555119127</v>
+        <v>0.4811203400383836</v>
       </c>
       <c r="R3" s="5">
         <v>11</v>
@@ -2216,16 +2216,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.2465610009057906</v>
+        <v>0.1320111827035362</v>
       </c>
       <c r="O4" s="5">
         <v>10</v>
       </c>
       <c r="P4" s="4">
-        <v>0.415590272258642</v>
+        <v>0.3951446345887865</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.415590272258642</v>
+        <v>0.3951446345887865</v>
       </c>
       <c r="R4" s="5">
         <v>10</v>
@@ -2275,16 +2275,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.5733582118084642</v>
+        <v>0.5799755712539536</v>
       </c>
       <c r="O5" s="5">
         <v>9</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2867026843785794</v>
+        <v>0.2856624820840504</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2867026843785794</v>
+        <v>0.2856624820840504</v>
       </c>
       <c r="R5" s="5">
         <v>9</v>
@@ -2457,22 +2457,22 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1976979036698612</v>
+        <v>0.08775626465944697</v>
       </c>
       <c r="O3" s="5">
         <v>13</v>
       </c>
       <c r="P3" s="4">
-        <v>0.7422566760382862</v>
+        <v>0.7229100421224169</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.6917381339367858</v>
+        <v>0.5083734097656532</v>
       </c>
       <c r="R3" s="5">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="S3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -2516,7 +2516,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.02944163986329171</v>
+        <v>-0.01164135100043495</v>
       </c>
       <c r="O4" s="5">
         <v>9</v>
@@ -2525,7 +2525,7 @@
         <v>0.4720091069726579</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.5141616616280861</v>
+        <v>0.5095968848654499</v>
       </c>
       <c r="R4" s="5">
         <v>9</v>
@@ -2575,13 +2575,13 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.6792075750392996</v>
+        <v>0.7853198174091176</v>
       </c>
       <c r="O5" s="5">
         <v>6</v>
       </c>
       <c r="P5" s="4">
-        <v>0.7905650001475932</v>
+        <v>0.8259357476041992</v>
       </c>
       <c r="Q5" s="4">
         <v>0.4321898275781375</v>
@@ -2757,16 +2757,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1569225104061067</v>
+        <v>-0.08052403902217975</v>
       </c>
       <c r="O3" s="5">
         <v>14</v>
       </c>
       <c r="P3" s="4">
-        <v>0.6835423627663946</v>
+        <v>0.6779951170104387</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.5718532490115074</v>
+        <v>0.5604527377455598</v>
       </c>
       <c r="R3" s="5">
         <v>14</v>
@@ -2816,7 +2816,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.04628124014020329</v>
+        <v>-0.003327386410546751</v>
       </c>
       <c r="O4" s="5">
         <v>10</v>
@@ -2875,16 +2875,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.4143912597681784</v>
+        <v>0.5127568569109826</v>
       </c>
       <c r="O5" s="5">
         <v>7</v>
       </c>
       <c r="P5" s="4">
-        <v>0.3696838888938582</v>
+        <v>0.3806133996875032</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.4005528978954113</v>
+        <v>0.3865006697321535</v>
       </c>
       <c r="R5" s="5">
         <v>7</v>
@@ -3057,16 +3057,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.006744980203566539</v>
+        <v>-0.0916379874243205</v>
       </c>
       <c r="O3" s="5">
         <v>11</v>
       </c>
       <c r="P3" s="4">
-        <v>0.6991707930634665</v>
+        <v>0.6779771759791818</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.6388654672081907</v>
+        <v>0.6278528925710547</v>
       </c>
       <c r="R3" s="5">
         <v>11</v>
@@ -3116,7 +3116,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.1817152576523792</v>
+        <v>0.1956496774682819</v>
       </c>
       <c r="O4" s="5">
         <v>7</v>
@@ -3125,7 +3125,7 @@
         <v>0.4656767095117204</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3722678278252493</v>
+        <v>0.3702771964229775</v>
       </c>
       <c r="R4" s="5">
         <v>7</v>
@@ -3175,13 +3175,13 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.5069914149463131</v>
+        <v>0.4588363447314805</v>
       </c>
       <c r="O5" s="5">
         <v>8</v>
       </c>
       <c r="P5" s="4">
-        <v>0.468470124433624</v>
+        <v>0.4631195610764204</v>
       </c>
       <c r="Q5" s="4">
         <v>0.3609456440039338</v>
@@ -3357,22 +3357,22 @@
         <v>2</v>
       </c>
       <c r="N3" s="4">
-        <v>1.027464642362869</v>
+        <v>0.7827005293478768</v>
       </c>
       <c r="O3" s="5">
         <v>10</v>
       </c>
       <c r="P3" s="4">
-        <v>1.188838738041853</v>
+        <v>1.082322990948918</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.6506935437994595</v>
+        <v>0.4590539544930106</v>
       </c>
       <c r="R3" s="5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -3416,7 +3416,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.7316787667620472</v>
+        <v>0.6205755453988786</v>
       </c>
       <c r="O4" s="5">
         <v>10</v>
@@ -3475,13 +3475,13 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>1.200275134758549</v>
+        <v>1.281582363350402</v>
       </c>
       <c r="O5" s="5">
         <v>6</v>
       </c>
       <c r="P5" s="4">
-        <v>1.532658712206701</v>
+        <v>1.559761121737318</v>
       </c>
       <c r="Q5" s="4">
         <v>0.4216414817850327</v>
@@ -3657,16 +3657,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2294774868872259</v>
+        <v>-0.2956165447994863</v>
       </c>
       <c r="O3" s="5">
         <v>13</v>
       </c>
       <c r="P3" s="4">
-        <v>0.6478892023122508</v>
+        <v>0.631871864857091</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.5443274322827021</v>
+        <v>0.5360211287440193</v>
       </c>
       <c r="R3" s="5">
         <v>13</v>
@@ -3716,16 +3716,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2157702498091137</v>
+        <v>-0.2858943642336964</v>
       </c>
       <c r="O4" s="5">
         <v>10</v>
       </c>
       <c r="P4" s="4">
-        <v>0.4369495328856166</v>
+        <v>0.4347536873668357</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.4369495328856166</v>
+        <v>0.4347536873668357</v>
       </c>
       <c r="R4" s="5">
         <v>10</v>
@@ -3775,16 +3775,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.06556628562684984</v>
+        <v>-0.105885166347079</v>
       </c>
       <c r="O5" s="5">
         <v>9</v>
       </c>
       <c r="P5" s="4">
-        <v>0.3359400808235408</v>
+        <v>0.3314602051879597</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.3359400808235408</v>
+        <v>0.3314602051879597</v>
       </c>
       <c r="R5" s="5">
         <v>9</v>
@@ -3957,13 +3957,13 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.7142360656257312</v>
+        <v>0.6203761843412243</v>
       </c>
       <c r="O3" s="5">
         <v>6</v>
       </c>
       <c r="P3" s="4">
-        <v>1.016215961431193</v>
+        <v>0.9849293343363574</v>
       </c>
       <c r="Q3" s="4">
         <v>0.3003772461047207</v>
@@ -4016,16 +4016,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.6909218912787572</v>
+        <v>0.7000712734147783</v>
       </c>
       <c r="O4" s="5">
         <v>6</v>
       </c>
       <c r="P4" s="4">
-        <v>0.468692564235475</v>
+        <v>0.4670278978199806</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.4772503658937495</v>
+        <v>0.4744759218679257</v>
       </c>
       <c r="R4" s="5">
         <v>6</v>
@@ -4255,16 +4255,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.396815333107944</v>
+        <v>-0.4168415849699407</v>
       </c>
       <c r="O3" s="5">
         <v>11</v>
       </c>
       <c r="P3" s="4">
-        <v>0.6031139359871855</v>
+        <v>0.6017788525297192</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.5712524270989939</v>
+        <v>0.5694318587479033</v>
       </c>
       <c r="R3" s="5">
         <v>11</v>
@@ -4314,7 +4314,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1928212624944033</v>
+        <v>-0.2662995219695858</v>
       </c>
       <c r="O4" s="5">
         <v>9</v>
@@ -4323,7 +4323,7 @@
         <v>0.4558833193630359</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3609615125198421</v>
+        <v>0.352797261467044</v>
       </c>
       <c r="R4" s="5">
         <v>9</v>
@@ -4373,16 +4373,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.07250149629827579</v>
+        <v>0.05404151636356858</v>
       </c>
       <c r="O5" s="5">
         <v>9</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2900492263587944</v>
+        <v>0.2879981174771602</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2900492263587944</v>
+        <v>0.2879981174771602</v>
       </c>
       <c r="R5" s="5">
         <v>9</v>
@@ -4519,13 +4519,13 @@
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <v>0.6316853652735562</v>
+        <v>0.6373345739774967</v>
       </c>
       <c r="I3" s="4">
-        <v>0.5284559359178584</v>
+        <v>0.521596182491645</v>
       </c>
       <c r="J3" s="4">
-        <v>0.5029850246453006</v>
+        <v>0.5433855899874132</v>
       </c>
       <c r="K3" s="4">
         <v>85.95938375350147</v>
@@ -4551,13 +4551,13 @@
         <v>18</v>
       </c>
       <c r="B4" s="3">
-        <v>79.41176470588235</v>
+        <v>82.35294117647058</v>
       </c>
       <c r="C4" s="3">
         <v>8.823529411764707</v>
       </c>
       <c r="D4" s="3">
-        <v>11.76470588235294</v>
+        <v>8.823529411764707</v>
       </c>
       <c r="E4" s="3">
         <v>0</v>
@@ -4566,16 +4566,16 @@
         <v>2.941176470588235</v>
       </c>
       <c r="G4" s="3">
-        <v>8.823529411764707</v>
+        <v>5.88235294117647</v>
       </c>
       <c r="H4" s="4">
-        <v>1.336142792843694</v>
+        <v>1.345449586028142</v>
       </c>
       <c r="I4" s="4">
-        <v>0.6792419459640576</v>
+        <v>0.6648706437261325</v>
       </c>
       <c r="J4" s="4">
-        <v>1.24986181517939</v>
+        <v>1.149839104195138</v>
       </c>
       <c r="K4" s="4">
         <v>87.71508603441376</v>
@@ -4619,13 +4619,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <v>0.5097155717600752</v>
+        <v>0.5081789302097661</v>
       </c>
       <c r="I5" s="4">
-        <v>0.4792968434351944</v>
+        <v>0.478771932731408</v>
       </c>
       <c r="J5" s="4">
-        <v>0.6982753462454127</v>
+        <v>0.6955333846668486</v>
       </c>
       <c r="K5" s="4">
         <v>89.47478991596641</v>
@@ -4669,13 +4669,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <v>0.4953361143870802</v>
+        <v>0.4897445483318179</v>
       </c>
       <c r="I6" s="4">
-        <v>0.5190673547604633</v>
+        <v>0.5034040758316697</v>
       </c>
       <c r="J6" s="4">
-        <v>0.5748498570197437</v>
+        <v>0.6060135671755669</v>
       </c>
       <c r="K6" s="4">
         <v>88.97859143657466</v>
@@ -4719,13 +4719,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <v>0.541193945096494</v>
+        <v>0.5141898100873314</v>
       </c>
       <c r="I7" s="4">
-        <v>0.4665699937087399</v>
+        <v>0.4456392522731988</v>
       </c>
       <c r="J7" s="4">
-        <v>0.5307000940482965</v>
+        <v>0.4535617553285964</v>
       </c>
       <c r="K7" s="4">
         <v>91.35454181672678</v>
@@ -4751,13 +4751,13 @@
         <v>22</v>
       </c>
       <c r="B8" s="3">
-        <v>91.17647058823529</v>
+        <v>82.35294117647058</v>
       </c>
       <c r="C8" s="3">
         <v>5.88235294117647</v>
       </c>
       <c r="D8" s="3">
-        <v>2.941176470588235</v>
+        <v>11.76470588235294</v>
       </c>
       <c r="E8" s="3">
         <v>0</v>
@@ -4766,16 +4766,16 @@
         <v>2.941176470588235</v>
       </c>
       <c r="G8" s="3">
-        <v>0</v>
+        <v>8.823529411764707</v>
       </c>
       <c r="H8" s="4">
-        <v>0.7368940773822578</v>
+        <v>0.7153683399752683</v>
       </c>
       <c r="I8" s="4">
-        <v>0.7194753021592244</v>
+        <v>0.5229655374987172</v>
       </c>
       <c r="J8" s="4">
-        <v>0.499880338074898</v>
+        <v>0.5907444528023273</v>
       </c>
       <c r="K8" s="4">
         <v>88.50240096038416</v>
@@ -4801,13 +4801,13 @@
         <v>23</v>
       </c>
       <c r="B9" s="3">
-        <v>85.29411764705883</v>
+        <v>76.47058823529412</v>
       </c>
       <c r="C9" s="3">
         <v>8.823529411764707</v>
       </c>
       <c r="D9" s="3">
-        <v>5.88235294117647</v>
+        <v>14.70588235294118</v>
       </c>
       <c r="E9" s="3">
         <v>2.941176470588235</v>
@@ -4816,16 +4816,16 @@
         <v>2.941176470588235</v>
       </c>
       <c r="G9" s="3">
-        <v>0</v>
+        <v>8.823529411764707</v>
       </c>
       <c r="H9" s="4">
-        <v>0.7813205247978028</v>
+        <v>0.7718643064648681</v>
       </c>
       <c r="I9" s="4">
-        <v>0.7844396291406315</v>
+        <v>0.5937810472821661</v>
       </c>
       <c r="J9" s="4">
-        <v>0.5364347048708735</v>
+        <v>0.5976141357970315</v>
       </c>
       <c r="K9" s="4">
         <v>86.38455382152864</v>
@@ -4869,13 +4869,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <v>0.4496667628891226</v>
+        <v>0.4350865332427761</v>
       </c>
       <c r="I10" s="4">
-        <v>0.4040840164208224</v>
+        <v>0.3938244141688846</v>
       </c>
       <c r="J10" s="4">
-        <v>0.6088899968444013</v>
+        <v>0.5657801042697187</v>
       </c>
       <c r="K10" s="4">
         <v>88.99659863945577</v>
@@ -4901,13 +4901,13 @@
         <v>25</v>
       </c>
       <c r="B11" s="3">
-        <v>82.35294117647058</v>
+        <v>79.41176470588235</v>
       </c>
       <c r="C11" s="3">
         <v>14.70588235294118</v>
       </c>
       <c r="D11" s="3">
-        <v>2.941176470588235</v>
+        <v>5.88235294117647</v>
       </c>
       <c r="E11" s="3">
         <v>0</v>
@@ -4916,16 +4916,16 @@
         <v>2.941176470588235</v>
       </c>
       <c r="G11" s="3">
-        <v>0</v>
+        <v>2.941176470588235</v>
       </c>
       <c r="H11" s="4">
-        <v>0.6755595944596827</v>
+        <v>0.6763871597059008</v>
       </c>
       <c r="I11" s="4">
-        <v>0.5790424879035648</v>
+        <v>0.4918515498683597</v>
       </c>
       <c r="J11" s="4">
-        <v>0.5757376061068264</v>
+        <v>0.6447379706477634</v>
       </c>
       <c r="K11" s="4">
         <v>88.57242897158864</v>
@@ -4969,13 +4969,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <v>0.5354505663355249</v>
+        <v>0.5358963578297445</v>
       </c>
       <c r="I12" s="4">
-        <v>0.4978982124289092</v>
+        <v>0.489576510659036</v>
       </c>
       <c r="J12" s="4">
-        <v>0.5799111514753003</v>
+        <v>0.606395117448871</v>
       </c>
       <c r="K12" s="4">
         <v>89.74389755902361</v>
@@ -5019,13 +5019,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <v>0.5694282385579946</v>
+        <v>0.5586617877791975</v>
       </c>
       <c r="I13" s="4">
-        <v>0.4815753879268582</v>
+        <v>0.4763802825105352</v>
       </c>
       <c r="J13" s="4">
-        <v>0.4612517947135663</v>
+        <v>0.4232693147179159</v>
       </c>
       <c r="K13" s="4">
         <v>88.68747498999606</v>
@@ -5051,13 +5051,13 @@
         <v>28</v>
       </c>
       <c r="B14" s="3">
-        <v>76.47058823529412</v>
+        <v>73.52941176470588</v>
       </c>
       <c r="C14" s="3">
         <v>0</v>
       </c>
       <c r="D14" s="3">
-        <v>23.52941176470588</v>
+        <v>26.47058823529412</v>
       </c>
       <c r="E14" s="3">
         <v>0</v>
@@ -5066,16 +5066,16 @@
         <v>23.52941176470588</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>2.941176470588235</v>
       </c>
       <c r="H14" s="4">
-        <v>1.068948998690853</v>
+        <v>1.029130924555016</v>
       </c>
       <c r="I14" s="4">
-        <v>0.5290208001425266</v>
+        <v>0.4551636382459276</v>
       </c>
       <c r="J14" s="4">
-        <v>0.6788024219311323</v>
+        <v>0.5771875483796062</v>
       </c>
       <c r="K14" s="4">
         <v>76.26450580232097</v>
@@ -5119,13 +5119,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <v>0.5032733556162292</v>
+        <v>0.4943751968593047</v>
       </c>
       <c r="I15" s="4">
-        <v>0.4521628961232237</v>
+        <v>0.4468422935635077</v>
       </c>
       <c r="J15" s="4">
-        <v>0.5842711163248419</v>
+        <v>0.5466959412951313</v>
       </c>
       <c r="K15" s="4">
         <v>90.41216486594638</v>
@@ -5169,13 +5169,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <v>0.9767204128625309</v>
+        <v>0.9624278813749579</v>
       </c>
       <c r="I16" s="4">
-        <v>0.4486046857706174</v>
+        <v>0.4474949081602878</v>
       </c>
       <c r="J16" s="4">
-        <v>0.6718133340614711</v>
+        <v>0.6399305679281441</v>
       </c>
       <c r="K16" s="4">
         <v>60.12605042016826</v>
@@ -5219,13 +5219,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <v>0.4769407432549204</v>
+        <v>0.4758087952608997</v>
       </c>
       <c r="I17" s="4">
-        <v>0.4187197706205745</v>
+        <v>0.4148589260939577</v>
       </c>
       <c r="J17" s="4">
-        <v>0.5966526322034327</v>
+        <v>0.5734261130279448</v>
       </c>
       <c r="K17" s="4">
         <v>89.61484593837534</v>
@@ -6152,13 +6152,13 @@
         <v>18</v>
       </c>
       <c r="B4" s="5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C4" s="5">
         <v>3</v>
       </c>
       <c r="D4" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E4" s="5">
         <v>0</v>
@@ -6167,7 +6167,7 @@
         <v>1</v>
       </c>
       <c r="G4" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H4" s="5">
         <v>0</v>
@@ -6328,13 +6328,13 @@
         <v>22</v>
       </c>
       <c r="B8" s="5">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C8" s="5">
         <v>2</v>
       </c>
       <c r="D8" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E8" s="5">
         <v>0</v>
@@ -6343,7 +6343,7 @@
         <v>1</v>
       </c>
       <c r="G8" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H8" s="5">
         <v>0</v>
@@ -6372,13 +6372,13 @@
         <v>23</v>
       </c>
       <c r="B9" s="5">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C9" s="5">
         <v>3</v>
       </c>
       <c r="D9" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E9" s="5">
         <v>1</v>
@@ -6387,7 +6387,7 @@
         <v>1</v>
       </c>
       <c r="G9" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H9" s="5">
         <v>1</v>
@@ -6460,13 +6460,13 @@
         <v>25</v>
       </c>
       <c r="B11" s="5">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C11" s="5">
         <v>5</v>
       </c>
       <c r="D11" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" s="5">
         <v>0</v>
@@ -6475,7 +6475,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" s="5">
         <v>0</v>
@@ -6592,13 +6592,13 @@
         <v>28</v>
       </c>
       <c r="B14" s="5">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C14" s="5">
         <v>0</v>
       </c>
       <c r="D14" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E14" s="5">
         <v>0</v>
@@ -6607,7 +6607,7 @@
         <v>8</v>
       </c>
       <c r="G14" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" s="5">
         <v>0</v>
@@ -6922,16 +6922,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.00934706011847714</v>
+        <v>0.1086837430029846</v>
       </c>
       <c r="O3" s="5">
         <v>11</v>
       </c>
       <c r="P3" s="4">
-        <v>0.6906173285289087</v>
+        <v>0.6984860487370061</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.6850728163029828</v>
+        <v>0.6743427432919408</v>
       </c>
       <c r="R3" s="5">
         <v>11</v>
@@ -6981,16 +6981,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.1715155102360285</v>
+        <v>0.1751539539977784</v>
       </c>
       <c r="O4" s="5">
         <v>10</v>
       </c>
       <c r="P4" s="4">
-        <v>0.4801664556054702</v>
+        <v>0.4801664556054703</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.4801664556054702</v>
+        <v>0.4801664556054703</v>
       </c>
       <c r="R4" s="5">
         <v>10</v>
@@ -7040,16 +7040,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.8016823846570073</v>
+        <v>0.8757246774695204</v>
       </c>
       <c r="O5" s="5">
         <v>7</v>
       </c>
       <c r="P5" s="4">
-        <v>0.7018197705902868</v>
+        <v>0.7100466920138994</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.3513286671875031</v>
+        <v>0.3407511967857155</v>
       </c>
       <c r="R5" s="5">
         <v>7</v>
@@ -7222,22 +7222,22 @@
         <v>2</v>
       </c>
       <c r="N3" s="4">
-        <v>0.6682889997292679</v>
+        <v>0.08350955687501482</v>
       </c>
       <c r="O3" s="5">
         <v>11</v>
       </c>
       <c r="P3" s="4">
-        <v>2.351328011243043</v>
+        <v>2.381096163594431</v>
       </c>
       <c r="Q3" s="4">
-        <v>1.022574719123698</v>
+        <v>0.9541705059212625</v>
       </c>
       <c r="R3" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S3" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -7281,16 +7281,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.02776903883099919</v>
+        <v>-0.1515824972656787</v>
       </c>
       <c r="O4" s="5">
         <v>10</v>
       </c>
       <c r="P4" s="4">
-        <v>0.6403178215914045</v>
+        <v>0.6356477941064469</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.6403178215914045</v>
+        <v>0.6356477941064469</v>
       </c>
       <c r="R4" s="5">
         <v>10</v>
@@ -7338,16 +7338,16 @@
         <v>9</v>
       </c>
       <c r="N5" s="4">
-        <v>4.605200028243833</v>
+        <v>4.521808986093788</v>
       </c>
       <c r="O5" s="5">
         <v>9</v>
       </c>
       <c r="P5" s="4">
-        <v>0.4173062857917691</v>
+        <v>0.4080406144417641</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.4173062857917691</v>
+        <v>0.4080406144417641</v>
       </c>
       <c r="R5" s="5">
         <v>9</v>
@@ -7520,16 +7520,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.338493848320026</v>
+        <v>-0.3537162587298326</v>
       </c>
       <c r="O3" s="5">
         <v>11</v>
       </c>
       <c r="P3" s="4">
-        <v>0.6113763410993092</v>
+        <v>0.6123911684599629</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.5398848584149571</v>
+        <v>0.5385010029231565</v>
       </c>
       <c r="R3" s="5">
         <v>11</v>
@@ -7579,7 +7579,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.02905986457585925</v>
+        <v>-0.09023389000890347</v>
       </c>
       <c r="O4" s="5">
         <v>10</v>
@@ -7638,13 +7638,13 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.3013663586571766</v>
+        <v>0.3688345817774916</v>
       </c>
       <c r="O5" s="5">
         <v>8</v>
       </c>
       <c r="P5" s="4">
-        <v>0.4405413025763004</v>
+        <v>0.4330448333407099</v>
       </c>
       <c r="Q5" s="4">
         <v>0.4707578021112369</v>
@@ -7820,16 +7820,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.02991345979129838</v>
+        <v>0.1833728682873925</v>
       </c>
       <c r="O3" s="5">
         <v>14</v>
       </c>
       <c r="P3" s="4">
-        <v>0.599933281316432</v>
+        <v>0.5821454575755467</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.6286416351423271</v>
+        <v>0.5986218662416576</v>
       </c>
       <c r="R3" s="5">
         <v>14</v>
@@ -7879,7 +7879,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.2142406898315604</v>
+        <v>0.2795255720147907</v>
       </c>
       <c r="O4" s="5">
         <v>9</v>
@@ -7888,7 +7888,7 @@
         <v>0.4947904790429704</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.4942234605507292</v>
+        <v>0.4869695847525924</v>
       </c>
       <c r="R4" s="5">
         <v>9</v>
@@ -7938,13 +7938,13 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.615856914442773</v>
+        <v>0.5391528042084133</v>
       </c>
       <c r="O5" s="5">
         <v>8</v>
       </c>
       <c r="P5" s="4">
-        <v>0.3216137643316159</v>
+        <v>0.3301364432465448</v>
       </c>
       <c r="Q5" s="4">
         <v>0.3552617450781526</v>
@@ -8120,16 +8120,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.07028798992642202</v>
+        <v>-0.04148372220697638</v>
       </c>
       <c r="O3" s="5">
         <v>13</v>
       </c>
       <c r="P3" s="4">
-        <v>0.6880071724976186</v>
+        <v>0.6592407339323187</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.56892013660413</v>
+        <v>0.5529237401262299</v>
       </c>
       <c r="R3" s="5">
         <v>13</v>
@@ -8179,16 +8179,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.123158023511175</v>
+        <v>-0.08967234376223132</v>
       </c>
       <c r="O4" s="5">
         <v>10</v>
       </c>
       <c r="P4" s="4">
-        <v>0.4550205418062364</v>
+        <v>0.4195181768984213</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.4550205418062364</v>
+        <v>0.4195181768984213</v>
       </c>
       <c r="R4" s="5">
         <v>10</v>
@@ -8238,16 +8238,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.4841041850268795</v>
+        <v>0.4383600034839219</v>
       </c>
       <c r="O5" s="5">
         <v>8</v>
       </c>
       <c r="P5" s="4">
-        <v>0.3922534586393501</v>
+        <v>0.3776289738889191</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.31468782638186</v>
+        <v>0.3039533037304949</v>
       </c>
       <c r="R5" s="5">
         <v>8</v>
